--- a/output/pdf_financials_xlsx/RZL.xlsx
+++ b/output/pdf_financials_xlsx/RZL.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.014174</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.024659</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.333981</v>
+        <v>-2.348155</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.793585</v>
+        <v>-4.818244</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.255575</v>
+        <v>-2.269749</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.716174</v>
+        <v>-4.740833</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.360177</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.3966</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.360177</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.3966</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.484081</v>
+        <v>0.123904</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.583719</v>
+        <v>0.187119</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/output/pdf_financials_xlsx/RZL.xlsx
+++ b/output/pdf_financials_xlsx/RZL.xlsx
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.00215</v>
       </c>
     </row>
     <row r="113">
@@ -3022,7 +3022,11 @@
           <t>Proceeds from sale of property and equipment 8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RZL.xlsx
+++ b/output/pdf_financials_xlsx/RZL.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.09735199999999999</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.143404</v>
       </c>
     </row>
     <row r="68">
